--- a/data/trans_camb/IP16_n_R2-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>0.1759495554543196</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.301899156753816</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.402806811063317</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.682127834573251</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.5976513417672233</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.504840389432401</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-2.347688410488218</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.8231550331957641</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.73682757050979</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.921340141737779</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.749680657194925</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-0.2841658260200411</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>3.02805265064491</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.41541723519636</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.453605806981064</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.993009275314156</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.536210542351227</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>5.977842924044897</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.05378751689243906</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1.009385651543378</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.2675283389930703</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.3207974626358442</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1412200503638302</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.5918729888617466</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.5078634579203215</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.2325944255821879</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.6636645403277435</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.4680347962783364</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4936468565055567</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1004859638757227</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>1.698885009783536</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3.940715763869628</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.4493755174603136</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1.936446123249741</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.507796528407479</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.849750919161428</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-1.294015331931615</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>5.058366986580668</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.524731847865433</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3.760870194753816</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.908757775309907</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>4.432749425658352</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-4.165779421888873</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.255998061978791</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.550036301880778</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.1876283908890392</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-3.765863519464252</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1.342851681277829</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>1.215021187010482</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>9.018587750805903</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.07324844712538664</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.57592631326332</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.2261353068724705</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>7.144261728612551</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.3616071151187534</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1.413539274298214</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.6233208869444521</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.9285061094543015</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.5003368934603754</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.16194317886253</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.8063103185987377</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.1838774693016354</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.8845739750373341</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.08428081215114588</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7545834586998047</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.2199357979855001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.7321709779775983</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>4.050962255880791</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.1043206353753227</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2.779272779841711</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.02675566757221714</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.410074839580796</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-0.5364466468533012</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>5.657794861260317</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.480332699302342</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>5.249851115446581</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-1.008284472690252</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>5.451579657538339</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-3.21373724293389</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2.211924329537427</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.02849548039759</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1.711152557097397</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-2.740090332832603</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>2.849986378899234</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>1.412692284733202</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9.903739895314162</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.7758714113039572</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>9.362371814199092</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.5364742591089324</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>8.127894599511846</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.2950065054404128</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>3.111374263050555</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.6273875338707872</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>2.224966824053199</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.4836722625790587</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2.615113035070574</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -912,14 +1025,21 @@
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="n">
+        <v>0.2912696251306703</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.2593515369406096</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.8938539813591447</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.7854555419930822</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -929,14 +1049,21 @@
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="n">
+        <v>16.32847687417595</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>2.088597448038843</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>9.893166437480932</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.6381247817405051</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>7.207455629100397</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1076,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-2.391825307543189</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>6.001891285305152</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.2716215724181715</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>7.730342467542702</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.202859870408028</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>6.803770512288512</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1102,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-6.067825011708116</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.114653454354364</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.807062655792317</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>2.485565013275969</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-3.599690501149621</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>3.246802681680484</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1128,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>11.70009214386203</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>4.422570857672814</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>12.33957713934443</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.9655095243062187</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>10.24110389059789</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1154,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.8060200170613526</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>2.02257434977604</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.1620847136611516</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>4.612926485181024</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.5053072426887547</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>2.858183735305216</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1018,14 +1181,17 @@
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="n">
+        <v>0.05888607850037046</v>
+      </c>
       <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="n">
+        <v>0.07757281051009095</v>
+      </c>
       <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="n">
+        <v>0.6358258463119214</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1035,14 +1201,15 @@
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="n">
+        <v>12.37311365144226</v>
+      </c>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="n">
+        <v>8.666573365247318</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1222,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.7061129062227566</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>5.014451039478097</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-1.516231630283883</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>4.181497179290977</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.101812845716287</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>4.608072728205316</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1248,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-2.132100357960389</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2.908160475132273</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.04788288479831</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1.9813199387872</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.151123526542797</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>3.162840814647809</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1274,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.5798816967530906</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>7.077188868119944</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.06364182246419942</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>6.383840499404167</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.001003589875850945</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>6.127319340219167</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1300,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.234780601907345</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>1.667291197920944</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.3972523419344832</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1.095551308974321</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.3237936482230992</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1.354190673800848</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1326,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.5628280560813064</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.7021901373803343</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.6258417648532778</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.4306962538050094</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.529012630635705</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.7780543265155514</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1352,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.2775102833960122</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>3.039029345378929</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.05991133993427352</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>2.042131721670419</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.01759155382556708</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>2.135154832268799</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1380,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
